--- a/data/데이터코드표.xlsx
+++ b/data/데이터코드표.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U105"/>
+  <dimension ref="A1:V105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,25 +500,30 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>OCR쪽</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>판정_자동</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>판정사유</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>이용조건</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>판정_수동</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -595,23 +600,24 @@
         <v>0</v>
       </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>본문 없음(초록만 제공)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>http://www.diabetesjournals.org/content/license</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
         <is>
           <t>출판사가 본문 XML 미제공</t>
         </is>
@@ -684,19 +690,20 @@
         <v>0</v>
       </c>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>CC BY-NC</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -765,19 +772,20 @@
         <v>0</v>
       </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
         <is>
           <t>CC BY-NC</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -846,19 +854,20 @@
         <v>0</v>
       </c>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
         <is>
           <t>CC BY-NC 4.0</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -927,19 +936,20 @@
         <v>0</v>
       </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
         <is>
           <t>CC BY-NC</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1008,19 +1018,20 @@
         <v>0</v>
       </c>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
         <is>
           <t>CC BY-NC 4.0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1089,19 +1100,20 @@
         <v>0</v>
       </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
         <is>
           <t>CC BY-NC 4.0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1170,19 +1182,20 @@
         <v>0</v>
       </c>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,19 +1264,20 @@
         <v>0</v>
       </c>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1336,19 +1350,20 @@
         <v>0</v>
       </c>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1421,19 +1436,20 @@
         <v>0</v>
       </c>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1506,19 +1522,20 @@
         <v>0</v>
       </c>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1591,19 +1608,20 @@
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1676,19 +1694,20 @@
         <v>0</v>
       </c>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1761,19 +1780,20 @@
         <v>0</v>
       </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1846,19 +1866,20 @@
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1931,19 +1952,20 @@
         <v>0</v>
       </c>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2016,19 +2038,20 @@
         <v>0</v>
       </c>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2101,19 +2124,20 @@
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2186,19 +2210,20 @@
         <v>0</v>
       </c>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2271,19 +2296,20 @@
         <v>0</v>
       </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2356,19 +2382,20 @@
         <v>0</v>
       </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2441,19 +2468,20 @@
         <v>0</v>
       </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2526,19 +2554,20 @@
         <v>0</v>
       </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2611,19 +2640,20 @@
         <v>0</v>
       </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2696,19 +2726,20 @@
         <v>0</v>
       </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr">
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2781,19 +2812,20 @@
         <v>0</v>
       </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr">
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2866,19 +2898,20 @@
         <v>0</v>
       </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr">
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2951,19 +2984,20 @@
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr">
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3036,19 +3070,20 @@
         <v>0</v>
       </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
         <is>
           <t>공공누리 확인</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3115,7 +3150,7 @@
         <v>135</v>
       </c>
       <c r="N32" t="n">
-        <v>63950</v>
+        <v>64359</v>
       </c>
       <c r="O32" t="n">
         <v>19</v>
@@ -3127,21 +3162,26 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>텍스트 없는 쪽 19개 → OCR 검토 | 유사: khepi-ob-002 83% | 유사: mohw-002 68%</t>
-        </is>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
+          <t>텍스트 없는 쪽 19개 중 1개 OCR (나머지는 표지·간지·빈 쪽) | 유사: khepi-ob-002 82% | 유사: mohw-002 67%</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3208,7 +3248,7 @@
         <v>131</v>
       </c>
       <c r="N33" t="n">
-        <v>62776</v>
+        <v>63144</v>
       </c>
       <c r="O33" t="n">
         <v>18</v>
@@ -3220,21 +3260,26 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>텍스트 없는 쪽 18개 → OCR 검토 | 유사: khepi-ob-001 83% | 유사: mohw-002 67% | 유사: mohw-006 83%</t>
-        </is>
-      </c>
       <c r="S33" t="inlineStr">
         <is>
+          <t>텍스트 없는 쪽 18개 중 1개 OCR (나머지는 표지·간지·빈 쪽) | 유사: khepi-ob-001 82% | 유사: mohw-002 66% | 유사: mohw-006 82%</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3301,7 +3346,7 @@
         <v>141</v>
       </c>
       <c r="N34" t="n">
-        <v>70797</v>
+        <v>71663</v>
       </c>
       <c r="O34" t="n">
         <v>13</v>
@@ -3313,21 +3358,26 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
+          <t>41,46</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>텍스트 없는 쪽 13개 → OCR 검토 | 유사: mohw-003 80% | 유사: mohw-007 87%</t>
-        </is>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
+          <t>텍스트 없는 쪽 13개 중 2개 OCR (나머지는 표지·간지·빈 쪽) | 유사: mohw-003 79% | 유사: mohw-007 86%</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3404,23 +3454,24 @@
           <t>1,2,3,8,9,26,27,41</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>텍스트 없는 쪽 8개 → OCR 검토</t>
-        </is>
-      </c>
       <c r="S35" t="inlineStr">
         <is>
+          <t>텍스트 없는 쪽 8개 → 표지·간지·빈 쪽</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3497,23 +3548,24 @@
           <t>1,2,4,6</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>텍스트 없는 쪽 4개 → OCR 검토</t>
-        </is>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
+          <t>텍스트 없는 쪽 4개 → 표지·간지·빈 쪽</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3580,7 +3632,7 @@
         <v>81</v>
       </c>
       <c r="N37" t="n">
-        <v>15198</v>
+        <v>36079</v>
       </c>
       <c r="O37" t="n">
         <v>46</v>
@@ -3592,21 +3644,26 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>1,4,5,7,9,11,15,17,18,19,20,21,25,27,29,31,33,35,37,39,41,43,45,47,49,51,53,55,57,59,61,65,67,69,71,73,75,77,79,81</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>텍스트 없는 쪽 46개 → OCR 검토</t>
-        </is>
-      </c>
       <c r="S37" t="inlineStr">
         <is>
+          <t>텍스트 없는 쪽 46개 중 40개 OCR (나머지는 표지·간지·빈 쪽)</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3679,19 +3736,20 @@
         <v>0</v>
       </c>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr">
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3768,23 +3826,24 @@
           <t>1,4,5,7,9,11,12,13,15,17,18,19,20,21,22,23,25,27,29,31,33,35,37,39,41,43,45,47,49,51,53,55,57,59,61,62,63,65,67,69,71,73,75,77,79,81</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>완전 중복: khepi-pa-004</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3851,7 +3910,7 @@
         <v>127</v>
       </c>
       <c r="N40" t="n">
-        <v>61321</v>
+        <v>61743</v>
       </c>
       <c r="O40" t="n">
         <v>16</v>
@@ -3863,21 +3922,26 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>텍스트 없는 쪽 16개 → OCR 검토 | 유사: khepi-ob-001 68% | 유사: khepi-ob-002 67% | 유사: mohw-006 68%</t>
-        </is>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
+          <t>텍스트 없는 쪽 16개 중 1개 OCR (나머지는 표지·간지·빈 쪽) | 유사: khepi-ob-001 67% | 유사: khepi-ob-002 66% | 유사: mohw-006 67%</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3944,7 +4008,7 @@
         <v>139</v>
       </c>
       <c r="N41" t="n">
-        <v>69918</v>
+        <v>70715</v>
       </c>
       <c r="O41" t="n">
         <v>15</v>
@@ -3956,21 +4020,26 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
+          <t>41,46</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>텍스트 없는 쪽 15개 → OCR 검토 | 유사: khepi-pa-001 80% | 유사: mohw-007 78%</t>
-        </is>
-      </c>
       <c r="S41" t="inlineStr">
         <is>
+          <t>텍스트 없는 쪽 15개 중 2개 OCR (나머지는 표지·간지·빈 쪽) | 유사: khepi-pa-001 79% | 유사: mohw-007 77%</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4047,23 +4116,24 @@
           <t>2,6,7,11,12,31,32,33,38,39,40,41,76,80,113,114,115,130</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>완전 중복: khepi-ob-002</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4136,23 +4206,24 @@
           <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80,81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99,100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138,139,140,141</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>텍스트 층 없는 PDF(141/141쪽) → OCR 필요</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4219,7 +4290,7 @@
         <v>135</v>
       </c>
       <c r="N44" t="n">
-        <v>63950</v>
+        <v>64359</v>
       </c>
       <c r="O44" t="n">
         <v>19</v>
@@ -4231,21 +4302,26 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>내용 중복: khepi-ob-001</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4312,7 +4388,7 @@
         <v>141</v>
       </c>
       <c r="N45" t="n">
-        <v>71399</v>
+        <v>71844</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
@@ -4324,21 +4400,26 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>텍스트 없는 쪽 10개 → OCR 검토 | 유사: khepi-pa-001 87% | 유사: mohw-003 78%</t>
-        </is>
-      </c>
       <c r="S45" t="inlineStr">
         <is>
+          <t>텍스트 없는 쪽 10개 중 1개 OCR (나머지는 표지·간지·빈 쪽) | 유사: khepi-pa-001 86% | 유사: mohw-003 77%</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4411,19 +4492,20 @@
         <v>0</v>
       </c>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr">
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4496,19 +4578,20 @@
         <v>0</v>
       </c>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr">
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/3.0/</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr">
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
         <is>
           <t>2026-10-01 운동 생리 기전 자료로 복원</t>
         </is>
@@ -4585,23 +4668,24 @@
         <v>0</v>
       </c>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr">
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
         <is>
           <t>http://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>주제 무관(기초의학·역학·편지) → 2026-09-30 PMCID 지정 목록에서 뺌</t>
         </is>
@@ -4678,23 +4762,24 @@
         <v>0</v>
       </c>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>본문 없음(초록만 제공)</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>http://creativecommons.org/licenses/by-nc/3.0/</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4767,19 +4852,20 @@
         <v>0</v>
       </c>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr">
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr">
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
         <is>
           <t>2026-10-01 운동 생리 기전 자료로 복원</t>
         </is>
@@ -4856,19 +4942,20 @@
         <v>0</v>
       </c>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr">
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr">
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
         <is>
           <t>2026-10-01 운동 생리 기전 자료로 복원</t>
         </is>
@@ -4945,19 +5032,20 @@
         <v>0</v>
       </c>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr">
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/3.0/</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5030,19 +5118,20 @@
         <v>0</v>
       </c>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr">
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/3.0/</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5115,19 +5204,20 @@
         <v>0</v>
       </c>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr">
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5200,19 +5290,20 @@
         <v>0</v>
       </c>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr">
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5285,19 +5376,20 @@
         <v>0</v>
       </c>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr">
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5370,19 +5462,20 @@
         <v>0</v>
       </c>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr">
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5455,19 +5548,20 @@
         <v>0</v>
       </c>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr">
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5540,19 +5634,20 @@
         <v>0</v>
       </c>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr">
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5625,19 +5720,20 @@
         <v>0</v>
       </c>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr">
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5710,19 +5806,20 @@
         <v>0</v>
       </c>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr">
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5795,19 +5892,20 @@
         <v>0</v>
       </c>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr">
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5880,19 +5978,20 @@
         <v>0</v>
       </c>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr">
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/3.0/</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5965,19 +6064,20 @@
         <v>0</v>
       </c>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr">
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6050,19 +6150,20 @@
         <v>0</v>
       </c>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr">
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6135,19 +6236,20 @@
         <v>0</v>
       </c>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr">
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6220,19 +6322,20 @@
         <v>0</v>
       </c>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr">
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6305,19 +6408,20 @@
         <v>0</v>
       </c>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr">
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6390,23 +6494,24 @@
         <v>0</v>
       </c>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr">
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/Open AccessThis article is distributed under the terms of the Creative Commo</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>주제 무관(기초의학·역학·편지) → 2026-09-30 PMCID 지정 목록에서 뺌</t>
         </is>
@@ -6483,23 +6588,24 @@
         <v>0</v>
       </c>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr">
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/This is an Open Access article distributed under the terms of the Creativ</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>주제 무관(기초의학·역학·편지) → 2026-09-30 PMCID 지정 목록에서 뺌</t>
         </is>
@@ -6576,19 +6682,20 @@
         <v>0</v>
       </c>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr">
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6661,19 +6768,20 @@
         <v>0</v>
       </c>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr">
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6746,19 +6854,20 @@
         <v>0</v>
       </c>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr">
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6831,19 +6940,20 @@
         <v>0</v>
       </c>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr">
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6916,19 +7026,20 @@
         <v>0</v>
       </c>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr">
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7001,19 +7112,20 @@
         <v>0</v>
       </c>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr">
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7086,19 +7198,20 @@
         <v>0</v>
       </c>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr">
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7171,19 +7284,20 @@
         <v>0</v>
       </c>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr">
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7256,19 +7370,20 @@
         <v>0</v>
       </c>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr">
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
         <is>
           <t>http://www.karger.com/Authors_Choice</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7341,19 +7456,20 @@
         <v>0</v>
       </c>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr">
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7426,19 +7542,20 @@
         <v>0</v>
       </c>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr">
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7511,19 +7628,20 @@
         <v>0</v>
       </c>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr">
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7596,19 +7714,20 @@
         <v>0</v>
       </c>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr">
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr">
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc-nd/3.0/</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7681,19 +7800,20 @@
         <v>0</v>
       </c>
       <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr">
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr">
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7766,19 +7886,20 @@
         <v>0</v>
       </c>
       <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr">
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr">
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7851,19 +7972,20 @@
         <v>0</v>
       </c>
       <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr">
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7936,19 +8058,20 @@
         <v>0</v>
       </c>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr">
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8021,19 +8144,20 @@
         <v>0</v>
       </c>
       <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr">
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8106,19 +8230,20 @@
         <v>0</v>
       </c>
       <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr">
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8191,19 +8316,20 @@
         <v>0</v>
       </c>
       <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr">
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr">
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8276,19 +8402,20 @@
         <v>0</v>
       </c>
       <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr">
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr">
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr">
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr">
         <is>
           <t>2026-10-01 운동 생리 기전 자료로 복원</t>
         </is>
@@ -8365,23 +8492,24 @@
         <v>0</v>
       </c>
       <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr">
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>본문 없음(초록만 제공)</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/This is an Open Access article distributed under the terms of the Creativ</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8454,23 +8582,24 @@
         <v>0</v>
       </c>
       <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr">
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr">
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/This is an open-access article distributed under the terms of the Creativ</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="V93" t="inlineStr">
         <is>
           <t>주제 무관(기초의학·역학·편지) → 2026-09-30 PMCID 지정 목록에서 뺌</t>
         </is>
@@ -8547,19 +8676,20 @@
         <v>0</v>
       </c>
       <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr">
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr">
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8632,19 +8762,20 @@
         <v>0</v>
       </c>
       <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr">
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr">
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr">
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr">
         <is>
           <t>2026-10-01 운동 생리 기전 자료로 복원</t>
         </is>
@@ -8721,19 +8852,20 @@
         <v>0</v>
       </c>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr">
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr">
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8806,19 +8938,20 @@
         <v>0</v>
       </c>
       <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr">
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr">
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8891,19 +9024,20 @@
         <v>0</v>
       </c>
       <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr">
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr">
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8976,19 +9110,20 @@
         <v>0</v>
       </c>
       <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr">
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr">
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9061,19 +9196,20 @@
         <v>0</v>
       </c>
       <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr">
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr">
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9146,19 +9282,20 @@
         <v>0</v>
       </c>
       <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr">
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr">
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9231,19 +9368,20 @@
         <v>0</v>
       </c>
       <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr">
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr">
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9316,19 +9454,20 @@
         <v>0</v>
       </c>
       <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr">
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr">
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9401,19 +9540,20 @@
         <v>0</v>
       </c>
       <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr">
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr">
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9490,23 +9630,24 @@
           <t>2,12,13,36,37</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>텍스트 없는 쪽 5개 → OCR 검토</t>
-        </is>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
+          <t>텍스트 없는 쪽 5개 → 표지·간지·빈 쪽</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
           <t>공공누리 확인 필요</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr">
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr">
         <is>
           <t>규칙 문서: 검색 대상 아님</t>
         </is>
@@ -9972,7 +10113,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>126726</v>
+        <v>127503</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -10009,7 +10150,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>127447</v>
+        <v>149194</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -10083,7 +10224,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>202638</v>
+        <v>204302</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -10371,7 +10512,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2805392</v>
+        <v>2829580</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
